--- a/Pedidos_Manutencao.xlsx
+++ b/Pedidos_Manutencao.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>EM EXECUCAO</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
